--- a/stories/arbres/TREE-REL-002.xlsx
+++ b/stories/arbres/TREE-REL-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le jardin, Kenzo veut l'arrosoir. Léa arrose encore les fleurs. Kenzo trépigne un peu. Papa tient le tuyau. Maman coupe du thym. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac à sable, Léa n'a pas fini le château. C'est le bac à sable. La cuillère tinte. Kenzo s'approche, sans courir. Maman n'est pas loin. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre n'a pas fini. Que fait-on ? Avec le bac à sable.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo retient le geste. Il respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2388,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes, après le bac à sable. Le lait est tiède. Kenzo montre les cubes à papa. Il nomme ce qu'il sent. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2581,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2750,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le rouge, après le bac à sable et les cubes. La tasse est encore tiède. On dit merci. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2917,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3084,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le bleu, après le bac à sable et les cubes. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. On écoute le silence une seconde. Kenzo est assis. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3251,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3418,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le vert, après le bac à sable et les cubes. Une abeille bourdonne loin. On attend un petit moment. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3585,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3752,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre, après le bac à sable. Le sable colle un peu aux doigts. On parle du livre. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3945,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4114,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le rouge, après le bac à sable et le livre. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4281,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4448,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le bleu, après le bac à sable et le livre. La fenêtre tremble un tout petit peu. On sourit un peu. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. On écoute le silence une seconde. Kenzo est assis. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4615,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4782,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le vert, après le bac à sable et le livre. Ça sent le savon de maman. On boit une gorgée d'eau. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4949,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5116,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette, après le bac à sable. Ça sent le thym du jardin. On parle de la dînette. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5309,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5478,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le rouge, après le bac à sable et la dînette. Un pigeon roucoule. On essuie une miette. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5645,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5812,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le bleu, après le bac à sable et la dînette. La cuillère tinte. On referme un livre. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. On écoute le silence une seconde. Kenzo est assis. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5979,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6146,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le vert, après le bac à sable et la dînette. Le ballon est un peu poudreux. On pose un jouet à sa place. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6313,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6480,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Au toboggan, Tom n'a pas encore glissé. Kenzo s'occupe du toboggan. La terre est un peu humide. Papa sourit. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre n'a pas fini. Que fait-on ? Avec le toboggan.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo répète le mot. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7025,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7192,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes, après le toboggan. La corde de la balançoire bouge. On parle des cubes. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7387,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7219,7 +7416,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le rouge, après le toboggan et les cubes. Une goutte de pluie sèche déjà. On marche tout doucement. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Papa dit : je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
+          <t>Kenzo rejoint le rouge, après le toboggan et les cubes. Une goutte de pluie sèche déjà. On marche tout doucement. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7357,6 +7554,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le rouge, après le toboggan et les cubes. Une goutte de pluie sèche déjà. On marche tout doucement. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.
+papa|Je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7722,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7889,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le bleu, après le toboggan et les cubes. Le banc est tiède. On se tait une seconde. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8056,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8223,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le vert, après le toboggan et les cubes. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8390,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8557,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre, après le toboggan. Le banc est tiède. On parle du livre. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8519,6 +8752,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8543,7 +8781,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le rouge, après le toboggan et le livre. Une feuille tourne et tombe. On s'assoit près de l'adulte. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Papa dit : je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+          <t>Kenzo rejoint le rouge, après le toboggan et le livre. Une feuille tourne et tombe. On s'assoit près de l'adulte. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8681,6 +8919,12 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le rouge, après le toboggan et le livre. Une feuille tourne et tombe. On s'assoit près de l'adulte. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.
+papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le bleu, après le toboggan et le livre. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le vert, après le toboggan et le livre. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette, après le toboggan. Un grillon chante, tout petit. La dînette reste à sa place. Kenzo aussi. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le rouge, après le toboggan et la dînette. Une plume vole. On range les chaussures. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo pose rouge et va vers papa. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10191,7 +10480,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le bleu, après le toboggan et la dînette. Le pain croustille. On met le doudou près de soi. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Papa dit : je t'ai entendu. Maman aussi. On se serre un peu.</t>
+          <t>Kenzo rejoint le bleu, après le toboggan et la dînette. Le pain croustille. On met le doudou près de soi. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10329,6 +10618,12 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le bleu, après le toboggan et la dînette. Le pain croustille. On met le doudou près de soi. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.
+papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10786,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10953,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le vert, après le toboggan et la dînette. La laine du doudou est douce. On écoute le cœur, tout doux. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11120,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10977,6 +11287,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Aux balançoires, Sami balance encore. Voilà les balançoires. Une plume vole. Kenzo pose les pieds par terre, près de papa. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre n'a pas fini. Que fait-on ? Avec les balançoires.</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11531,7 +11861,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a choisi les cubes, après les balançoires. Le sable est un peu frais. Kenzo touche les cubes tout doucement. Papa dit : je suis là. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+          <t>Kenzo a choisi les cubes, après les balançoires. Le sable est un peu frais. Kenzo touche les cubes tout doucement. Je suis là. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11669,6 +11999,13 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi les cubes, après les balançoires. Le sable est un peu frais. Kenzo touche les cubes tout doucement.
+papa|Je suis là.
+narrateur|Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12194,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12363,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le rouge, après les balançoires et les cubes. Un galet est lisse dans la main. On secoue les mains, loin. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12530,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12697,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le bleu, après les balançoires et les cubes. Le train souffle au loin. On pose le sac. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12864,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13031,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le vert, après les balançoires et les cubes. Une vache meugle, loin. On dit le mot de l'émotion. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13198,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13365,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le livre, après les balançoires. Un grillon chante, tout petit. On parle du livre. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13558,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13727,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le rouge, après les balançoires et le livre. Un grillon chante, tout petit. On invite d'une petite voix. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13894,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14061,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le bleu, après les balançoires et le livre. Le bois de la table est lisse. On attend la réponse. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14228,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13855,7 +14257,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rejoint le vert, après les balançoires et le livre. Une goutte tombe dans l'évier. On propose une autre idée. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Papa dit : je t'ai entendu. Maman aussi. On respire.</t>
+          <t>Kenzo rejoint le vert, après les balançoires et le livre. Une goutte tombe dans l'évier. On propose une autre idée. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Je t'ai entendu. Maman aussi. On respire.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13993,6 +14395,12 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le vert, après les balançoires et le livre. Une goutte tombe dans l'évier. On propose une autre idée. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.
+papa|Je t'ai entendu. Maman aussi. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14563,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14730,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la dînette, après les balançoires. Le lait est tiède. On parle de la dînette. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14923,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15092,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le rouge, après les balançoires et la dînette. Le toboggan est un peu froid. On va vers papa ou maman. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo pose rouge et va vers papa. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15259,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15426,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le bleu, après les balançoires et la dînette. La clochette de la porte tinte. On dit stop, tout clair. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo pose bleu et va vers papa. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15593,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15760,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le vert, après les balançoires et la dînette. Ça sent le thym du jardin. On s'éloigne d'un pas. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo pose vert et va vers papa. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15927,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16023,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-002.xlsx
+++ b/stories/arbres/TREE-REL-002.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Dans le jardin, Kenzo veut l'arrosoir. Léa arrose encore les fleurs. Kenzo trépigne un peu. Papa tient le tuyau. Maman coupe du thym. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Au bac à sable, Léa n'a pas fini le château. C'est le bac à sable. La cuillère tinte. Kenzo s'approche, sans courir. Maman n'est pas loin. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|L'autre n'a pas fini. Que fait-on ? Avec le bac à sable.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Oui. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo retient le geste. Il respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2393,6 +2404,7 @@
           <t>narrateur|Kenzo a choisi les cubes, après le bac à sable. Le lait est tiède. Kenzo montre les cubes à papa. Il nomme ce qu'il sent. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2755,6 +2768,7 @@
           <t>narrateur|Kenzo rejoint le rouge, après le bac à sable et les cubes. La tasse est encore tiède. On dit merci. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3104,7 @@
           <t>narrateur|Kenzo rejoint le bleu, après le bac à sable et les cubes. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. On écoute le silence une seconde. Kenzo est assis. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3272,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3440,7 @@
           <t>narrateur|Kenzo rejoint le vert, après le bac à sable et les cubes. Une abeille bourdonne loin. On attend un petit moment. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3757,6 +3776,7 @@
           <t>narrateur|Kenzo a choisi le livre, après le bac à sable. Le sable colle un peu aux doigts. On parle du livre. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3952,6 +3972,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4119,6 +4140,7 @@
           <t>narrateur|Kenzo rejoint le rouge, après le bac à sable et le livre. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4286,6 +4308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4453,6 +4476,7 @@
           <t>narrateur|Kenzo rejoint le bleu, après le bac à sable et le livre. La fenêtre tremble un tout petit peu. On sourit un peu. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. On écoute le silence une seconde. Kenzo est assis. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4620,6 +4644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4787,6 +4812,7 @@
           <t>narrateur|Kenzo rejoint le vert, après le bac à sable et le livre. Ça sent le savon de maman. On boit une gorgée d'eau. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4954,6 +4980,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5121,6 +5148,7 @@
           <t>narrateur|Kenzo a choisi la dînette, après le bac à sable. Ça sent le thym du jardin. On parle de la dînette. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5316,6 +5344,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5483,6 +5512,7 @@
           <t>narrateur|Kenzo rejoint le rouge, après le bac à sable et la dînette. Un pigeon roucoule. On essuie une miette. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5650,6 +5680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5817,6 +5848,7 @@
           <t>narrateur|Kenzo rejoint le bleu, après le bac à sable et la dînette. La cuillère tinte. On referme un livre. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. On écoute le silence une seconde. Kenzo est assis. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5984,6 +6016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6151,6 +6184,7 @@
           <t>narrateur|Kenzo rejoint le vert, après le bac à sable et la dînette. Le ballon est un peu poudreux. On pose un jouet à sa place. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6318,6 +6352,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6485,6 +6520,7 @@
           <t>narrateur|Au toboggan, Tom n'a pas encore glissé. Kenzo s'occupe du toboggan. La terre est un peu humide. Papa sourit. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6704,7 @@
           <t>narrateur|L'autre n'a pas fini. Que fait-on ? Avec le toboggan.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6876,7 @@
           <t>narrateur|Oui. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo répète le mot. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7030,6 +7068,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7197,6 +7236,7 @@
           <t>narrateur|Kenzo a choisi les cubes, après le toboggan. La corde de la balançoire bouge. On parle des cubes. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7392,6 +7432,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7560,6 +7601,7 @@
 papa|Je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7727,6 +7769,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7894,6 +7937,7 @@
           <t>narrateur|Kenzo rejoint le bleu, après le toboggan et les cubes. Le banc est tiède. On se tait une seconde. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8061,6 +8105,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8228,6 +8273,7 @@
           <t>narrateur|Kenzo rejoint le vert, après le toboggan et les cubes. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8395,6 +8441,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8562,6 +8609,7 @@
           <t>narrateur|Kenzo a choisi le livre, après le toboggan. Le banc est tiède. On parle du livre. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8757,6 +8805,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
 papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Kenzo rejoint le bleu, après le toboggan et le livre. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Kenzo rejoint le vert, après le toboggan et le livre. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Kenzo a choisi la dînette, après le toboggan. Un grillon chante, tout petit. La dînette reste à sa place. Kenzo aussi. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Kenzo rejoint le rouge, après le toboggan et la dînette. Une plume vole. On range les chaussures. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo pose rouge et va vers papa. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10624,6 +10683,7 @@
 papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10791,6 +10851,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10958,6 +11019,7 @@
           <t>narrateur|Kenzo rejoint le vert, après le toboggan et la dînette. La laine du doudou est douce. On écoute le cœur, tout doux. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11125,6 +11187,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
           <t>narrateur|Aux balançoires, Sami balance encore. Voilà les balançoires. Une plume vole. Kenzo pose les pieds par terre, près de papa. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|L'autre n'a pas fini. Que fait-on ? Avec les balançoires.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12006,6 +12073,7 @@
 narrateur|Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12201,6 +12269,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12368,6 +12437,7 @@
           <t>narrateur|Kenzo rejoint le rouge, après les balançoires et les cubes. Un galet est lisse dans la main. On secoue les mains, loin. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12535,6 +12605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12702,6 +12773,7 @@
           <t>narrateur|Kenzo rejoint le bleu, après les balançoires et les cubes. Le train souffle au loin. On pose le sac. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12869,6 +12941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13036,6 +13109,7 @@
           <t>narrateur|Kenzo rejoint le vert, après les balançoires et les cubes. Une vache meugle, loin. On dit le mot de l'émotion. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo serre la main de papa, tout doux. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13203,6 +13277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13370,6 +13445,7 @@
           <t>narrateur|Kenzo a choisi le livre, après les balançoires. Un grillon chante, tout petit. On parle du livre. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13565,6 +13641,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13732,6 +13809,7 @@
           <t>narrateur|Kenzo rejoint le rouge, après les balançoires et le livre. Un grillon chante, tout petit. On invite d'une petite voix. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13899,6 +13977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14066,6 +14145,7 @@
           <t>narrateur|Kenzo rejoint le bleu, après les balançoires et le livre. Le bois de la table est lisse. On attend la réponse. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo boit une gorgée. Il se sent plus léger. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14233,6 +14313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14401,6 +14482,7 @@
 papa|Je t'ai entendu. Maman aussi. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14568,6 +14650,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14735,6 +14818,7 @@
           <t>narrateur|Kenzo a choisi la dînette, après les balançoires. Le lait est tiède. On parle de la dînette. Kenzo écoute jusqu'au bout. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14930,6 +15014,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15097,6 +15182,7 @@
           <t>narrateur|Kenzo rejoint le rouge, après les balançoires et la dînette. Le toboggan est un peu froid. On va vers papa ou maman. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo pose rouge et va vers papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15264,6 +15350,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15431,6 +15518,7 @@
           <t>narrateur|Kenzo rejoint le bleu, après les balançoires et la dînette. La clochette de la porte tinte. On dit stop, tout clair. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo pose bleu et va vers papa. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15598,6 +15686,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15765,6 +15854,7 @@
           <t>narrateur|Kenzo rejoint le vert, après les balançoires et la dînette. Ça sent le thym du jardin. On s'éloigne d'un pas. Kenzo attend. L'autre finit. Puis mon tour. Il joue après, près de papa. Kenzo pose vert et va vers papa. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15932,6 +16022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15950,7 +16041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16030,6 +16121,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16231,6 +16336,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
